--- a/survey_templates/037_repair_request_survey--survey_templates.xlsx
+++ b/survey_templates/037_repair_request_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1115,8 +1115,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'location_4'}</t>
+          <t>location_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Location 4'}</t>
+          <t>Location 4</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'issue_type_1'}</t>
+          <t>issue_type_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Issue Type 1'}</t>
+          <t>Issue Type 1</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'issue_type_2'}</t>
+          <t>issue_type_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Issue Type 2'}</t>
+          <t>Issue Type 2</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'issue_type_3'}</t>
+          <t>issue_type_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Issue Type 3'}</t>
+          <t>Issue Type 3</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'issue_severity_1'}</t>
+          <t>issue_severity_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Issue Severity 1'}</t>
+          <t>Issue Severity 1</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'issue_severity_2'}</t>
+          <t>issue_severity_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Issue Severity 2'}</t>
+          <t>Issue Severity 2</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'issue_severity_3'}</t>
+          <t>issue_severity_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Issue Severity 3'}</t>
+          <t>Issue Severity 3</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'repair_type_1'}</t>
+          <t>repair_type_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Repair Type 1'}</t>
+          <t>Repair Type 1</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'repair_type_2'}</t>
+          <t>repair_type_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Repair Type 2'}</t>
+          <t>Repair Type 2</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'repair_type_3'}</t>
+          <t>repair_type_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Repair Type 3'}</t>
+          <t>Repair Type 3</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'repair_outcome_1'}</t>
+          <t>repair_outcome_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Repair Outcome 1'}</t>
+          <t>Repair Outcome 1</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'repair_outcome_2'}</t>
+          <t>repair_outcome_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Repair Outcome 2'}</t>
+          <t>Repair Outcome 2</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'repair_outcome_3'}</t>
+          <t>repair_outcome_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Repair Outcome 3'}</t>
+          <t>Repair Outcome 3</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'issue_type_1'}</t>
+          <t>issue_type_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Issue Type 1'}</t>
+          <t>Issue Type 1</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'issue_type_2'}</t>
+          <t>issue_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Issue Type 2'}</t>
+          <t>Issue Type 2</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'issue_severity_1'}</t>
+          <t>issue_severity_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Issue Severity 1'}</t>
+          <t>Issue Severity 1</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'repair_outcome_1'}</t>
+          <t>repair_outcome_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Repair Outcome 1'}</t>
+          <t>Repair Outcome 1</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'repair_outcome_2'}</t>
+          <t>repair_outcome_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Repair Outcome 2'}</t>
+          <t>Repair Outcome 2</t>
         </is>
       </c>
     </row>
